--- a/features/security/delivered/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SwdlSecureLib_20260917.xlsx
+++ b/features/security/delivered/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SwdlSecureLib_20260917.xlsx
@@ -8001,7 +8001,70 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-001</t>
+          <t xml:space="preserve">CFTS084-134520
+CFTS084-134521
+CFTS084-134522
+CFTS084-134523
+CFTS084-134524
+CFTS084-134525
+CFTS084-134526
+CFTS084-134529
+CFTS084-134531
+CFTS084-134532
+CFTS084-134533
+CFTS084-134534
+CFTS084-134535
+CFTS084-134536
+CFTS084-134537
+CFTS084-134538
+CFTS084-134539
+CFTS084-134541
+CFTS084-134542
+CFTS084-134543
+CFTS084-134565
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134584
+CFTS084-134585
+CFTS084-134586
+CFTS084-134587
+CFTS084-134588
+CFTS084-134589
+CFTS084-134590
+CFTS084-134591
+CFTS084-134592
+CFTS084-134593
+CFTS084-134595
+CFTS084-134596
+CFTS084-134597
+CFTS084-134598
+CFTS084-134599
+CFTS084-134600
+CFTS084-134601
+CFTS084-134602
+CFTS084-134603
+CFTS084-134604
+CFTS084-134605
+CFTS084-134607
+CFTS084-134608
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613
+CFTS084-134804
+CFTS084-134823
+CFTS084-134824
+CFTS084-134825
+CFTS084-134827
+CFTS084-134828
+CFTS084-134841
+CFTS084-134849</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8139,7 +8202,70 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-001</t>
+          <t xml:space="preserve">CFTS084-134520
+CFTS084-134521
+CFTS084-134522
+CFTS084-134523
+CFTS084-134524
+CFTS084-134525
+CFTS084-134526
+CFTS084-134529
+CFTS084-134531
+CFTS084-134532
+CFTS084-134533
+CFTS084-134534
+CFTS084-134535
+CFTS084-134536
+CFTS084-134537
+CFTS084-134538
+CFTS084-134539
+CFTS084-134541
+CFTS084-134542
+CFTS084-134543
+CFTS084-134565
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134584
+CFTS084-134585
+CFTS084-134586
+CFTS084-134587
+CFTS084-134588
+CFTS084-134589
+CFTS084-134590
+CFTS084-134591
+CFTS084-134592
+CFTS084-134593
+CFTS084-134595
+CFTS084-134596
+CFTS084-134597
+CFTS084-134598
+CFTS084-134599
+CFTS084-134600
+CFTS084-134601
+CFTS084-134602
+CFTS084-134603
+CFTS084-134604
+CFTS084-134605
+CFTS084-134607
+CFTS084-134608
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613
+CFTS084-134804
+CFTS084-134823
+CFTS084-134824
+CFTS084-134825
+CFTS084-134827
+CFTS084-134828
+CFTS084-134841
+CFTS084-134849</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8277,7 +8403,16 @@
       </c>
       <c r="N12" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-002</t>
+          <t xml:space="preserve">CFTS084-134565
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582</t>
         </is>
       </c>
       <c r="O12" s="81" t="inlineStr">
@@ -8415,7 +8550,21 @@
       </c>
       <c r="N13" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-003</t>
+          <t xml:space="preserve">CFTS084-134531
+CFTS084-134534
+CFTS084-134535
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613</t>
         </is>
       </c>
       <c r="O13" s="177" t="inlineStr">
@@ -8554,7 +8703,21 @@
       </c>
       <c r="N14" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-003</t>
+          <t xml:space="preserve">CFTS084-134531
+CFTS084-134534
+CFTS084-134535
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613</t>
         </is>
       </c>
       <c r="O14" s="177" t="inlineStr">
@@ -8693,7 +8856,21 @@
       </c>
       <c r="N15" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-003</t>
+          <t xml:space="preserve">CFTS084-134531
+CFTS084-134534
+CFTS084-134535
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613</t>
         </is>
       </c>
       <c r="O15" s="177" t="inlineStr">
@@ -8832,7 +9009,19 @@
       </c>
       <c r="N16" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-004</t>
+          <t xml:space="preserve">CFTS084-134531
+CFTS084-134534
+CFTS084-134535
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613</t>
         </is>
       </c>
       <c r="O16" s="177" t="inlineStr">
@@ -8971,7 +9160,19 @@
       </c>
       <c r="N17" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-004</t>
+          <t xml:space="preserve">CFTS084-134531
+CFTS084-134534
+CFTS084-134535
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613</t>
         </is>
       </c>
       <c r="O17" s="81" t="inlineStr">
@@ -9109,7 +9310,19 @@
       </c>
       <c r="N18" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-004</t>
+          <t xml:space="preserve">CFTS084-134531
+CFTS084-134534
+CFTS084-134535
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582
+CFTS084-134609
+CFTS084-134612
+CFTS084-134613</t>
         </is>
       </c>
       <c r="O18" s="81" t="inlineStr">
@@ -9247,7 +9460,16 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-005</t>
+          <t xml:space="preserve">CFTS084-134565
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9385,7 +9607,16 @@
       </c>
       <c r="N20" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">SWE1_SwdlSecureLib_FM-WI-FSM-037-A03_SWE1-SRA-SECURITY-SWDL-005</t>
+          <t xml:space="preserve">CFTS084-134565
+CFTS084-134566
+CFTS084-134567
+CFTS084-134571
+CFTS084-134577
+CFTS084-134578
+CFTS084-134579
+CFTS084-134580
+CFTS084-134581
+CFTS084-134582</t>
         </is>
       </c>
       <c r="O20" s="81" t="inlineStr">

--- a/features/security/delivered/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SwdlSecureLib_20260917.xlsx
+++ b/features/security/delivered/FM-WI-FSM-036-A01 STLA 測試用例規範與結果_SWQT STLA Test Case Specification & Result_SWQT_Security_SwdlSecureLib_20260917.xlsx
@@ -8001,70 +8001,70 @@
       </c>
       <c r="N10" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134520
-CFTS084-134521
-CFTS084-134522
-CFTS084-134523
-CFTS084-134524
-CFTS084-134525
-CFTS084-134526
-CFTS084-134529
-CFTS084-134531
-CFTS084-134532
-CFTS084-134533
-CFTS084-134534
-CFTS084-134535
-CFTS084-134536
-CFTS084-134537
-CFTS084-134538
-CFTS084-134539
-CFTS084-134541
-CFTS084-134542
-CFTS084-134543
-CFTS084-134565
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134584
-CFTS084-134585
-CFTS084-134586
-CFTS084-134587
-CFTS084-134588
-CFTS084-134589
-CFTS084-134590
-CFTS084-134591
-CFTS084-134592
-CFTS084-134593
-CFTS084-134595
-CFTS084-134596
-CFTS084-134597
-CFTS084-134598
-CFTS084-134599
-CFTS084-134600
-CFTS084-134601
-CFTS084-134602
-CFTS084-134603
-CFTS084-134604
-CFTS084-134605
-CFTS084-134607
-CFTS084-134608
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613
-CFTS084-134804
-CFTS084-134823
-CFTS084-134824
-CFTS084-134825
-CFTS084-134827
-CFTS084-134828
-CFTS084-134841
-CFTS084-134849</t>
+          <t xml:space="preserve">CFTS084-4949510
+CFTS084-4949511
+CFTS084-4949512
+CFTS084-4949513
+CFTS084-4949516
+CFTS084-4949521
+CFTS084-4949522
+CFTS084-4949529
+CFTS084-4949531
+CFTS084-4949532
+CFTS084-4949533
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949538
+CFTS084-4949540
+CFTS084-4949541
+CFTS084-4949542
+CFTS084-4949545
+CFTS084-4949546
+CFTS084-4949547
+CFTS084-4949587
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949614
+CFTS084-4949615
+CFTS084-4949617
+CFTS084-4949618
+CFTS084-4949619
+CFTS084-4949620
+CFTS084-4949621
+CFTS084-4949622
+CFTS084-4949623
+CFTS084-4949624
+CFTS084-4949627
+CFTS084-4949628
+CFTS084-4949629
+CFTS084-4949630
+CFTS084-4949631
+CFTS084-4949632
+CFTS084-4949633
+CFTS084-4949634
+CFTS084-4949635
+CFTS084-4949636
+CFTS084-4949637
+CFTS084-4949639
+CFTS084-4949640
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646
+CFTS084-4949853
+CFTS084-4949878
+CFTS084-4949879
+CFTS084-4949880
+CFTS084-4949882
+CFTS084-4949883
+CFTS084-4949896
+CFTS084-4949905</t>
         </is>
       </c>
       <c r="O10" s="81" t="inlineStr">
@@ -8202,70 +8202,70 @@
       </c>
       <c r="N11" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134520
-CFTS084-134521
-CFTS084-134522
-CFTS084-134523
-CFTS084-134524
-CFTS084-134525
-CFTS084-134526
-CFTS084-134529
-CFTS084-134531
-CFTS084-134532
-CFTS084-134533
-CFTS084-134534
-CFTS084-134535
-CFTS084-134536
-CFTS084-134537
-CFTS084-134538
-CFTS084-134539
-CFTS084-134541
-CFTS084-134542
-CFTS084-134543
-CFTS084-134565
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134584
-CFTS084-134585
-CFTS084-134586
-CFTS084-134587
-CFTS084-134588
-CFTS084-134589
-CFTS084-134590
-CFTS084-134591
-CFTS084-134592
-CFTS084-134593
-CFTS084-134595
-CFTS084-134596
-CFTS084-134597
-CFTS084-134598
-CFTS084-134599
-CFTS084-134600
-CFTS084-134601
-CFTS084-134602
-CFTS084-134603
-CFTS084-134604
-CFTS084-134605
-CFTS084-134607
-CFTS084-134608
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613
-CFTS084-134804
-CFTS084-134823
-CFTS084-134824
-CFTS084-134825
-CFTS084-134827
-CFTS084-134828
-CFTS084-134841
-CFTS084-134849</t>
+          <t xml:space="preserve">CFTS084-4949510
+CFTS084-4949511
+CFTS084-4949512
+CFTS084-4949513
+CFTS084-4949516
+CFTS084-4949521
+CFTS084-4949522
+CFTS084-4949529
+CFTS084-4949531
+CFTS084-4949532
+CFTS084-4949533
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949538
+CFTS084-4949540
+CFTS084-4949541
+CFTS084-4949542
+CFTS084-4949545
+CFTS084-4949546
+CFTS084-4949547
+CFTS084-4949587
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949614
+CFTS084-4949615
+CFTS084-4949617
+CFTS084-4949618
+CFTS084-4949619
+CFTS084-4949620
+CFTS084-4949621
+CFTS084-4949622
+CFTS084-4949623
+CFTS084-4949624
+CFTS084-4949627
+CFTS084-4949628
+CFTS084-4949629
+CFTS084-4949630
+CFTS084-4949631
+CFTS084-4949632
+CFTS084-4949633
+CFTS084-4949634
+CFTS084-4949635
+CFTS084-4949636
+CFTS084-4949637
+CFTS084-4949639
+CFTS084-4949640
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646
+CFTS084-4949853
+CFTS084-4949878
+CFTS084-4949879
+CFTS084-4949880
+CFTS084-4949882
+CFTS084-4949883
+CFTS084-4949896
+CFTS084-4949905</t>
         </is>
       </c>
       <c r="O11" s="81" t="inlineStr">
@@ -8403,16 +8403,16 @@
       </c>
       <c r="N12" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134565
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582</t>
+          <t xml:space="preserve">CFTS084-4949587
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611</t>
         </is>
       </c>
       <c r="O12" s="81" t="inlineStr">
@@ -8550,21 +8550,21 @@
       </c>
       <c r="N13" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134531
-CFTS084-134534
-CFTS084-134535
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613</t>
+          <t xml:space="preserve">CFTS084-4949531
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646</t>
         </is>
       </c>
       <c r="O13" s="177" t="inlineStr">
@@ -8703,21 +8703,21 @@
       </c>
       <c r="N14" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134531
-CFTS084-134534
-CFTS084-134535
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613</t>
+          <t xml:space="preserve">CFTS084-4949531
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646</t>
         </is>
       </c>
       <c r="O14" s="177" t="inlineStr">
@@ -8856,21 +8856,21 @@
       </c>
       <c r="N15" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134531
-CFTS084-134534
-CFTS084-134535
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613</t>
+          <t xml:space="preserve">CFTS084-4949531
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646</t>
         </is>
       </c>
       <c r="O15" s="177" t="inlineStr">
@@ -9009,19 +9009,19 @@
       </c>
       <c r="N16" s="177" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134531
-CFTS084-134534
-CFTS084-134535
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613</t>
+          <t xml:space="preserve">CFTS084-4949531
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646</t>
         </is>
       </c>
       <c r="O16" s="177" t="inlineStr">
@@ -9160,19 +9160,19 @@
       </c>
       <c r="N17" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134531
-CFTS084-134534
-CFTS084-134535
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613</t>
+          <t xml:space="preserve">CFTS084-4949531
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646</t>
         </is>
       </c>
       <c r="O17" s="81" t="inlineStr">
@@ -9310,19 +9310,19 @@
       </c>
       <c r="N18" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134531
-CFTS084-134534
-CFTS084-134535
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582
-CFTS084-134609
-CFTS084-134612
-CFTS084-134613</t>
+          <t xml:space="preserve">CFTS084-4949531
+CFTS084-4949534
+CFTS084-4949535
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611
+CFTS084-4949642
+CFTS084-4949645
+CFTS084-4949646</t>
         </is>
       </c>
       <c r="O18" s="81" t="inlineStr">
@@ -9460,16 +9460,16 @@
       </c>
       <c r="N19" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134565
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582</t>
+          <t xml:space="preserve">CFTS084-4949587
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611</t>
         </is>
       </c>
       <c r="O19" s="81" t="inlineStr">
@@ -9607,16 +9607,16 @@
       </c>
       <c r="N20" s="81" t="inlineStr">
         <is>
-          <t xml:space="preserve">CFTS084-134565
-CFTS084-134566
-CFTS084-134567
-CFTS084-134571
-CFTS084-134577
-CFTS084-134578
-CFTS084-134579
-CFTS084-134580
-CFTS084-134581
-CFTS084-134582</t>
+          <t xml:space="preserve">CFTS084-4949587
+CFTS084-4949588
+CFTS084-4949593
+CFTS084-4949599
+CFTS084-4949606
+CFTS084-4949607
+CFTS084-4949608
+CFTS084-4949609
+CFTS084-4949610
+CFTS084-4949611</t>
         </is>
       </c>
       <c r="O20" s="81" t="inlineStr">
